--- a/data/dividends_info_20260705.xlsx
+++ b/data/dividends_info_20260705.xlsx
@@ -4275,7 +4275,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4336,14 +4336,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4353,14 +4353,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4394,7 +4394,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4455,14 +4455,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4472,14 +4472,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4523,14 +4523,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4676,14 +4676,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4693,14 +4693,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4727,14 +4727,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4785,7 +4785,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4795,14 +4795,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4846,14 +4846,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4863,14 +4863,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4887,7 +4887,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4938,7 +4938,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4965,14 +4965,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5006,7 +5006,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5091,7 +5091,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5152,14 +5152,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5176,7 +5176,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5203,14 +5203,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5261,7 +5261,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5271,14 +5271,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5288,14 +5288,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5322,14 +5322,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5380,7 +5380,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5424,14 +5424,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5448,7 +5448,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5492,14 +5492,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5509,14 +5509,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5533,7 +5533,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5584,7 +5584,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5601,7 +5601,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5645,14 +5645,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5662,14 +5662,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5696,14 +5696,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5720,7 +5720,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5730,14 +5730,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5754,7 +5754,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5805,7 +5805,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5822,7 +5822,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6019,14 +6019,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6060,7 +6060,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6077,7 +6077,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6087,14 +6087,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6138,14 +6138,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6155,14 +6155,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6189,14 +6189,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6234,265 +6234,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DATALOGIC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SAFILO GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>